--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484079_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484079_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1735</v>
+        <v>6.0699</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4132</v>
+        <v>5.3938</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7603</v>
+        <v>0.6761</v>
       </c>
       <c r="G2" t="n">
         <v>1.1071</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1444</v>
+        <v>-0.248</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0258</v>
+        <v>-0.0452</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1186</v>
+        <v>-0.2028</v>
       </c>
       <c r="V2" t="n">
         <v>4.4173</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2259</v>
+        <v>2.7679</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3419</v>
+        <v>1.9961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.7718</v>
       </c>
       <c r="G3" t="n">
         <v>2.8338</v>
@@ -688,13 +688,13 @@
         <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2629</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6746</v>
+        <v>0.3288</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5883</v>
+        <v>0.4761</v>
       </c>
       <c r="V3" t="n">
         <v>-1.6644</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7783</v>
+        <v>1.3276</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0157</v>
+        <v>1.6976</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2374</v>
+        <v>-0.3701</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3965</v>
+        <v>1.7325</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5391</v>
+        <v>0.5639</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1425</v>
+        <v>1.1686</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4128</v>
+        <v>1.7542</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4128</v>
+        <v>1.1492</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0163</v>
+        <v>-0.0216</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1263</v>
+        <v>-0.5853</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1425</v>
+        <v>0.5637</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5796</v>
+        <v>0.2225</v>
       </c>
       <c r="T4" t="n">
-        <v>2.222</v>
+        <v>0.1418</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3576</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2893</v>
+        <v>1.0616</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7194</v>
+        <v>1.3832</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0087</v>
+        <v>-0.3216</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7444</v>
+        <v>-0.3965</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0989</v>
+        <v>-0.5391</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6455</v>
+        <v>0.1425</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3595</v>
+        <v>-0.4128</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5563</v>
+        <v>-0.4128</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8032</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6151</v>
+        <v>0.0163</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4573</v>
+        <v>-0.1263</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.3725</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.5467</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1741</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>2.304</v>
+        <v>0.863</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2018</v>
+        <v>0.5896</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1022</v>
+        <v>0.2734</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3866</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6526</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.727</v>
+        <v>0.4549</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1251</v>
+        <v>-0.0623</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3981</v>
+        <v>0.5172</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7325</v>
+        <v>0.4081</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5639</v>
+        <v>0.136</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1686</v>
+        <v>0.2721</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7542</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1492</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0216</v>
+        <v>0.4081</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5853</v>
+        <v>0.136</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5637</v>
+        <v>0.2721</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3781</v>
+        <v>0.0468</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4307</v>
+        <v>-0.0623</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0526</v>
+        <v>0.1091</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4268</v>
+        <v>-0.0016</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0623</v>
+        <v>-2.3089</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4892</v>
+        <v>2.3073</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4081</v>
+        <v>2.7444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.136</v>
+        <v>1.0989</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2721</v>
+        <v>1.6455</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.3595</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.5563</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.8032</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4081</v>
+        <v>-0.6151</v>
       </c>
       <c r="N7" t="n">
-        <v>0.136</v>
+        <v>-1.4573</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2721</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-3.3725</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-6.5467</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.1741</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0187</v>
+        <v>1.0131</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0623</v>
+        <v>0.6123</v>
       </c>
       <c r="U7" t="n">
-        <v>0.081</v>
+        <v>0.4009</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3866</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6526</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1811</v>
+        <v>-0.083</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2851</v>
+        <v>-0.0187</v>
       </c>
       <c r="F8" t="n">
-        <v>0.104</v>
+        <v>-0.0643</v>
       </c>
       <c r="G8" t="n">
         <v>0.8413</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5112</v>
+        <v>0.6093</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3117</v>
+        <v>-0.0453</v>
       </c>
       <c r="U8" t="n">
-        <v>0.823</v>
+        <v>0.6546</v>
       </c>
       <c r="V8" t="n">
         <v>-1.9303</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1248</v>
+        <v>-0.5293</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3037</v>
+        <v>-2.4478</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4286</v>
+        <v>1.9185</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1702</v>
+        <v>0.324</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.139</v>
+        <v>0.3175</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0312</v>
+        <v>0.0065</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1259</v>
+        <v>-0.7248</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3937</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5195</v>
+        <v>-1.3604</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0443</v>
+        <v>1.0488</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5327</v>
+        <v>-0.3181</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5117</v>
+        <v>1.3669</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3968</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3806</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5299</v>
+        <v>0.1403</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0284</v>
+        <v>0.1418</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5584</v>
+        <v>-0.0015</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4085</v>
+        <v>-0.7952</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.6745</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6042</v>
+        <v>-1.0243</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3264</v>
+        <v>0.264</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7222</v>
+        <v>-1.2883</v>
       </c>
       <c r="G10" t="n">
-        <v>0.324</v>
+        <v>-2.1702</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3175</v>
+        <v>-1.139</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0065</v>
+        <v>-1.0312</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7248</v>
+        <v>-0.1259</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.3937</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3604</v>
+        <v>-0.5195</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0488</v>
+        <v>-2.0443</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3181</v>
+        <v>-1.5327</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3669</v>
+        <v>-0.5117</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1984</v>
+        <v>1.9838</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1903</v>
+        <v>-0.3968</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9347</v>
+        <v>-0.4293</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7368</v>
+        <v>-0.0112</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1979</v>
+        <v>-0.4181</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7952</v>
+        <v>-0.4085</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6745</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1206</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3147</v>
+        <v>-3.1566</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5368</v>
+        <v>-3.4348</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2221</v>
+        <v>0.2782</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2445</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5464</v>
+        <v>-0.3883</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.238</v>
+        <v>-0.136</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3084</v>
+        <v>-0.2523</v>
       </c>
       <c r="V11" t="n">
         <v>0.0713</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4823</v>
+        <v>-4.1099</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0601</v>
+        <v>-2.8561</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4221</v>
+        <v>-1.2538</v>
       </c>
       <c r="G12" t="n">
         <v>1.1286</v>
@@ -1390,13 +1390,13 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4206</v>
+        <v>-0.0482</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1247</v>
+        <v>0.0794</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2959</v>
+        <v>-0.1276</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4129</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0354</v>
+        <v>-5.2756</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.3214</v>
+        <v>-6.0947</v>
       </c>
       <c r="F13" t="n">
-        <v>0.286</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-6.3086</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6818</v>
+        <v>0.078</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3456</v>
+        <v>-0.1189</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3362</v>
+        <v>0.1969</v>
       </c>
       <c r="V13" t="n">
         <v>1.3518</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.121700000000001</v>
+        <v>-2.4984</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.111899999999999</v>
+        <v>-6.488599999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9903</v>
+        <v>3.990100000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6803000000000003</v>
+        <v>-0.6803000000000008</v>
       </c>
       <c r="I14" t="n">
         <v>0.6802000000000001</v>
@@ -1534,7 +1534,7 @@
         <v>-7.9181</v>
       </c>
       <c r="O14" t="n">
-        <v>5.6041</v>
+        <v>5.604099999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-0.9920000000000002</v>
@@ -1546,13 +1546,13 @@
         <v>18.8463</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0405</v>
+        <v>2.664099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8511999999999998</v>
+        <v>1.4748</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1893</v>
+        <v>1.1894</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1704</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3372</v>
+        <v>5.8958</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7626</v>
+        <v>3.6606</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5746</v>
+        <v>2.2353</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6801</v>
@@ -1624,13 +1624,13 @@
         <v>2.579</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0187</v>
+        <v>0.5399</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4479</v>
+        <v>0.3459</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4666</v>
+        <v>0.194</v>
       </c>
       <c r="V15" t="n">
         <v>6.4408</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.291</v>
+        <v>3.1822</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3894</v>
+        <v>0.5935</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9016</v>
+        <v>2.5888</v>
       </c>
       <c r="G16" t="n">
         <v>1.9713</v>
@@ -1702,13 +1702,13 @@
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9986</v>
+        <v>0.8899</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0057</v>
+        <v>0.2098</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9929</v>
+        <v>0.68</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8692</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5366</v>
+        <v>2.3843</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3769</v>
+        <v>-0.1916</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1596</v>
+        <v>2.5759</v>
       </c>
       <c r="G17" t="n">
-        <v>0.586</v>
+        <v>1.8657</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1679</v>
+        <v>-0.3432</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5819</v>
+        <v>2.2089</v>
       </c>
       <c r="J17" t="n">
-        <v>1.07</v>
+        <v>1.6793</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9499</v>
+        <v>-0.0955</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8799</v>
+        <v>1.7748</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.484</v>
+        <v>0.1865</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.782</v>
+        <v>-0.2477</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2981</v>
+        <v>0.4341</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>2.736</v>
+        <v>0.717</v>
       </c>
       <c r="T17" t="n">
-        <v>1.933</v>
+        <v>-0.153</v>
       </c>
       <c r="U17" t="n">
-        <v>0.803</v>
+        <v>0.87</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3417</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7384</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.606</v>
+        <v>1.2332</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8863</v>
+        <v>0.2546</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2803</v>
+        <v>0.9786</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1334</v>
+        <v>0.586</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.736</v>
+        <v>2.1679</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8694</v>
+        <v>-1.5819</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7713</v>
+        <v>1.07</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7311</v>
+        <v>2.9499</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>-1.8799</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6379</v>
+        <v>-0.484</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4671</v>
+        <v>-0.782</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8292</v>
+        <v>0.2981</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1903</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.055</v>
+        <v>1.4326</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.306</v>
+        <v>0.8107</v>
       </c>
       <c r="U18" t="n">
-        <v>0.251</v>
+        <v>0.6219</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3373</v>
+        <v>0.6032</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4129</v>
+        <v>2.3417</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.0757</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3692</v>
+        <v>1.1834</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2936</v>
+        <v>1.5802</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6628</v>
+        <v>-0.3968</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8657</v>
+        <v>0.1334</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3432</v>
+        <v>-0.736</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2089</v>
+        <v>0.8694</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6793</v>
+        <v>0.7713</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0955</v>
+        <v>0.7311</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7748</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1865</v>
+        <v>-0.6379</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2477</v>
+        <v>-1.4671</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4341</v>
+        <v>0.8292</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2981</v>
+        <v>-0.4775</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.255</v>
+        <v>-0.6121</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0432</v>
+        <v>0.1345</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>2.4129</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.266</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0164</v>
+        <v>0.5528</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1721</v>
+        <v>-0.9681</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1885</v>
+        <v>1.5209</v>
       </c>
       <c r="G20" t="n">
         <v>0.1235</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7023</v>
+        <v>-0.1658</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0788</v>
+        <v>0.2536</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6897</v>
+        <v>-0.7619</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4816</v>
+        <v>-1.314</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1713</v>
+        <v>0.5521</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8535</v>
+        <v>-0.8767</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0857</v>
+        <v>-0.7407</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9393</v>
+        <v>-0.136</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2727</v>
+        <v>-1.093</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9529</v>
+        <v>-0.4128</v>
       </c>
       <c r="L21" t="n">
         <v>-0.6802</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1262</v>
+        <v>0.2163</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8672</v>
+        <v>-0.3279</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2591</v>
+        <v>0.5442</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6297</v>
+        <v>-0.8771</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0056</v>
+        <v>-0.221</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6241</v>
+        <v>-0.6561</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7696</v>
+        <v>-0.9116</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5181</v>
+        <v>0.1756</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7484</v>
+        <v>-1.0872</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8767</v>
+        <v>-0.8535</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7407</v>
+        <v>0.0857</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.136</v>
+        <v>-0.9393</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.093</v>
+        <v>0.2727</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4128</v>
+        <v>0.9529</v>
       </c>
       <c r="L22" t="n">
         <v>-0.6802</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2163</v>
+        <v>-1.1262</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3279</v>
+        <v>-0.8672</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5442</v>
+        <v>-0.2591</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8848</v>
+        <v>-0.8516</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4251</v>
+        <v>-0.3117</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4597</v>
+        <v>-0.5399</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8304</v>
+        <v>-1.3255</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6756</v>
+        <v>-0.8594000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1548</v>
+        <v>-0.4661</v>
       </c>
       <c r="G23" t="n">
         <v>2.9012</v>
@@ -2248,13 +2248,13 @@
         <v>2.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2753</v>
+        <v>0.2296</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0995</v>
+        <v>-0.2833</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1758</v>
+        <v>0.5128</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0757</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7448</v>
+        <v>-6.2704</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2276</v>
+        <v>-6.9215</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4828</v>
+        <v>0.6511</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1708</v>
@@ -2326,13 +2326,13 @@
         <v>2.579</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9113</v>
+        <v>-1.4368</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8615</v>
+        <v>-0.5554</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0498</v>
+        <v>-0.8815</v>
       </c>
       <c r="V24" t="n">
         <v>-0.266</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.121899999999998</v>
+        <v>5.162299999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9902</v>
+        <v>-3.9901</v>
       </c>
       <c r="F25" t="n">
-        <v>7.1119</v>
+        <v>9.152599999999998</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2392,10 +2392,10 @@
         <v>-7.237900000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>4.923900000000001</v>
+        <v>4.9239</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9918999999999996</v>
+        <v>0.9919</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.8464</v>
@@ -2404,13 +2404,13 @@
         <v>19.8385</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.0406</v>
+        <v>0.0002000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1896</v>
+        <v>-1.1895</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8511</v>
+        <v>1.1893</v>
       </c>
       <c r="V25" t="n">
         <v>4.170400000000001</v>
